--- a/enums/CL709.PartyIdentifierType.v2023p03.xlsx
+++ b/enums/CL709.PartyIdentifierType.v2023p03.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="26529"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29231"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Werkbestanden\AgroConnect\Coderingslijsten AgroConnect\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Werkbestanden\AgroConnect\Coderingslijsten AgroConnect\Codelijsten_AgroConnect_master\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12865A7D-CEC3-40DD-B590-D9B95A2F04D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDB08EFB-DFDB-49AB-9068-8A31ED13B1C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -345,18 +345,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -381,18 +375,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="14" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -704,14 +696,14 @@
   <dimension ref="A1:M40"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="17" style="9" customWidth="1"/>
-    <col min="2" max="2" width="11" style="9" customWidth="1"/>
-    <col min="3" max="3" width="42.28515625" style="9" customWidth="1"/>
-    <col min="4" max="4" width="34" style="9" customWidth="1"/>
-    <col min="5" max="5" width="13.28515625" style="9" customWidth="1"/>
-    <col min="6" max="7" width="11.42578125" style="9" customWidth="1"/>
-    <col min="8" max="8" width="48.42578125" style="9" customWidth="1"/>
-    <col min="9" max="13" width="9.140625" style="7"/>
+    <col min="1" max="1" width="17" style="7" customWidth="1"/>
+    <col min="2" max="2" width="11" style="7" customWidth="1"/>
+    <col min="3" max="3" width="42.28515625" style="7" customWidth="1"/>
+    <col min="4" max="4" width="34" style="7" customWidth="1"/>
+    <col min="5" max="5" width="13.28515625" style="7" customWidth="1"/>
+    <col min="6" max="7" width="11.42578125" style="7" customWidth="1"/>
+    <col min="8" max="8" width="48.42578125" style="7" customWidth="1"/>
+    <col min="9" max="13" width="9.140625" style="5"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -931,8 +923,8 @@
       <c r="E12" s="4">
         <v>43769</v>
       </c>
-      <c r="F12" s="8"/>
-      <c r="G12" s="8"/>
+      <c r="F12" s="6"/>
+      <c r="G12" s="6"/>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
@@ -950,8 +942,8 @@
       <c r="E13" s="4">
         <v>43769</v>
       </c>
-      <c r="F13" s="8"/>
-      <c r="G13" s="8"/>
+      <c r="F13" s="6"/>
+      <c r="G13" s="6"/>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
@@ -969,8 +961,8 @@
       <c r="E14" s="4">
         <v>43769</v>
       </c>
-      <c r="F14" s="8"/>
-      <c r="G14" s="8"/>
+      <c r="F14" s="6"/>
+      <c r="G14" s="6"/>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
@@ -988,8 +980,8 @@
       <c r="E15" s="4">
         <v>43769</v>
       </c>
-      <c r="F15" s="8"/>
-      <c r="G15" s="8"/>
+      <c r="F15" s="6"/>
+      <c r="G15" s="6"/>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
@@ -1007,8 +999,8 @@
       <c r="E16" s="4">
         <v>43769</v>
       </c>
-      <c r="F16" s="8"/>
-      <c r="G16" s="8"/>
+      <c r="F16" s="6"/>
+      <c r="G16" s="6"/>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
@@ -1026,8 +1018,8 @@
       <c r="E17" s="4">
         <v>43769</v>
       </c>
-      <c r="F17" s="8"/>
-      <c r="G17" s="8"/>
+      <c r="F17" s="6"/>
+      <c r="G17" s="6"/>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
@@ -1045,8 +1037,8 @@
       <c r="E18" s="4">
         <v>43769</v>
       </c>
-      <c r="F18" s="8"/>
-      <c r="G18" s="8"/>
+      <c r="F18" s="6"/>
+      <c r="G18" s="6"/>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
@@ -1064,8 +1056,8 @@
       <c r="E19" s="4">
         <v>43769</v>
       </c>
-      <c r="F19" s="8"/>
-      <c r="G19" s="8"/>
+      <c r="F19" s="6"/>
+      <c r="G19" s="6"/>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
@@ -1083,8 +1075,8 @@
       <c r="E20" s="4">
         <v>43769</v>
       </c>
-      <c r="F20" s="8"/>
-      <c r="G20" s="8"/>
+      <c r="F20" s="6"/>
+      <c r="G20" s="6"/>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
@@ -1102,8 +1094,8 @@
       <c r="E21" s="4">
         <v>43769</v>
       </c>
-      <c r="F21" s="8"/>
-      <c r="G21" s="8"/>
+      <c r="F21" s="6"/>
+      <c r="G21" s="6"/>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
@@ -1121,8 +1113,8 @@
       <c r="E22" s="4">
         <v>43769</v>
       </c>
-      <c r="F22" s="8"/>
-      <c r="G22" s="8"/>
+      <c r="F22" s="6"/>
+      <c r="G22" s="6"/>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
@@ -1140,8 +1132,8 @@
       <c r="E23" s="4">
         <v>43811</v>
       </c>
-      <c r="F23" s="8"/>
-      <c r="G23" s="8"/>
+      <c r="F23" s="6"/>
+      <c r="G23" s="6"/>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
@@ -1159,8 +1151,8 @@
       <c r="E24" s="4">
         <v>43818</v>
       </c>
-      <c r="F24" s="8"/>
-      <c r="G24" s="8"/>
+      <c r="F24" s="6"/>
+      <c r="G24" s="6"/>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
@@ -1178,8 +1170,8 @@
       <c r="E25" s="4">
         <v>43818</v>
       </c>
-      <c r="F25" s="8"/>
-      <c r="G25" s="8"/>
+      <c r="F25" s="6"/>
+      <c r="G25" s="6"/>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
@@ -1197,8 +1189,8 @@
       <c r="E26" s="4">
         <v>43885</v>
       </c>
-      <c r="F26" s="8"/>
-      <c r="G26" s="8"/>
+      <c r="F26" s="6"/>
+      <c r="G26" s="6"/>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
@@ -1216,9 +1208,9 @@
       <c r="E27" s="4">
         <v>43885</v>
       </c>
-      <c r="F27" s="8"/>
-      <c r="G27" s="8"/>
-      <c r="H27" s="9" t="s">
+      <c r="F27" s="6"/>
+      <c r="G27" s="6"/>
+      <c r="H27" s="7" t="s">
         <v>72</v>
       </c>
     </row>
@@ -1238,8 +1230,8 @@
       <c r="E28" s="4">
         <v>43888</v>
       </c>
-      <c r="F28" s="8"/>
-      <c r="G28" s="8"/>
+      <c r="F28" s="6"/>
+      <c r="G28" s="6"/>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
@@ -1257,8 +1249,8 @@
       <c r="E29" s="4">
         <v>44042</v>
       </c>
-      <c r="F29" s="8"/>
-      <c r="G29" s="8"/>
+      <c r="F29" s="6"/>
+      <c r="G29" s="6"/>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
@@ -1276,8 +1268,8 @@
       <c r="E30" s="4">
         <v>44252</v>
       </c>
-      <c r="F30" s="8"/>
-      <c r="G30" s="8"/>
+      <c r="F30" s="6"/>
+      <c r="G30" s="6"/>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
@@ -1295,9 +1287,9 @@
       <c r="E31" s="4">
         <v>44253</v>
       </c>
-      <c r="F31" s="8"/>
-      <c r="G31" s="8"/>
-      <c r="H31" s="9" t="s">
+      <c r="F31" s="6"/>
+      <c r="G31" s="6"/>
+      <c r="H31" s="7" t="s">
         <v>71</v>
       </c>
     </row>
@@ -1317,8 +1309,8 @@
       <c r="E32" s="4">
         <v>44299</v>
       </c>
-      <c r="F32" s="8"/>
-      <c r="G32" s="8"/>
+      <c r="F32" s="6"/>
+      <c r="G32" s="6"/>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
@@ -1336,8 +1328,8 @@
       <c r="E33" s="4">
         <v>44710</v>
       </c>
-      <c r="F33" s="8"/>
-      <c r="G33" s="8"/>
+      <c r="F33" s="6"/>
+      <c r="G33" s="6"/>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
@@ -1355,69 +1347,69 @@
       <c r="E34" s="4">
         <v>44979</v>
       </c>
-      <c r="F34" s="8"/>
-      <c r="G34" s="8"/>
+      <c r="F34" s="6"/>
+      <c r="G34" s="6"/>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A35" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="B35" s="5" t="s">
+      <c r="A35" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B35" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="C35" s="5" t="s">
+      <c r="C35" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D35" s="5" t="s">
+      <c r="D35" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="E35" s="6">
+      <c r="E35" s="4">
         <v>45090</v>
       </c>
-      <c r="F35" s="8"/>
-      <c r="G35" s="8"/>
+      <c r="F35" s="6"/>
+      <c r="G35" s="6"/>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A36" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="B36" s="5" t="s">
+      <c r="A36" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B36" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="C36" s="5" t="s">
+      <c r="C36" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="D36" s="5" t="s">
+      <c r="D36" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="E36" s="6">
+      <c r="E36" s="4">
         <v>45126</v>
       </c>
-      <c r="F36" s="8"/>
-      <c r="G36" s="8"/>
-      <c r="H36" s="10" t="s">
+      <c r="F36" s="6"/>
+      <c r="G36" s="6"/>
+      <c r="H36" s="8" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="E37" s="8"/>
-      <c r="F37" s="8"/>
-      <c r="G37" s="8"/>
+      <c r="E37" s="6"/>
+      <c r="F37" s="6"/>
+      <c r="G37" s="6"/>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="E38" s="8"/>
-      <c r="F38" s="8"/>
-      <c r="G38" s="8"/>
+      <c r="E38" s="6"/>
+      <c r="F38" s="6"/>
+      <c r="G38" s="6"/>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="E39" s="8"/>
-      <c r="F39" s="8"/>
-      <c r="G39" s="8"/>
+      <c r="E39" s="6"/>
+      <c r="F39" s="6"/>
+      <c r="G39" s="6"/>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="E40" s="8"/>
-      <c r="F40" s="8"/>
-      <c r="G40" s="8"/>
+      <c r="E40" s="6"/>
+      <c r="F40" s="6"/>
+      <c r="G40" s="6"/>
     </row>
   </sheetData>
   <hyperlinks>
